--- a/0_raw_data/io_overview.xlsx
+++ b/0_raw_data/io_overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linuslindquist/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linuslindquist/Desktop/BA/0_raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA19668-D12C-F34C-9985-E6E1BFC8FB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CC8881-CCE5-5641-BE22-B11E200A1131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="25100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3902,7 +3902,7 @@
         <v>109718.322</v>
       </c>
       <c r="H192">
-        <f>F192</f>
+        <f t="shared" ref="H192:H200" si="0">F192</f>
         <v>109718.322</v>
       </c>
       <c r="S192" s="10" t="s">
@@ -3920,7 +3920,7 @@
         <v>92130.319000000003</v>
       </c>
       <c r="H193">
-        <f>F193</f>
+        <f t="shared" si="0"/>
         <v>92130.319000000003</v>
       </c>
       <c r="S193" s="10" t="s">
@@ -3938,7 +3938,7 @@
         <v>67168.456000000006</v>
       </c>
       <c r="H194">
-        <f>F194</f>
+        <f t="shared" si="0"/>
         <v>67168.456000000006</v>
       </c>
       <c r="S194" s="10" t="s">
@@ -3956,7 +3956,7 @@
         <v>16846.954000000002</v>
       </c>
       <c r="H195">
-        <f>F195</f>
+        <f t="shared" si="0"/>
         <v>16846.954000000002</v>
       </c>
       <c r="S195" s="10" t="s">
@@ -3974,7 +3974,7 @@
         <v>47059.222000000002</v>
       </c>
       <c r="H196">
-        <f>F196</f>
+        <f t="shared" si="0"/>
         <v>47059.222000000002</v>
       </c>
       <c r="S196" s="10" t="s">
@@ -3992,7 +3992,7 @@
         <v>-75.516999999999996</v>
       </c>
       <c r="H197">
-        <f>F197</f>
+        <f t="shared" si="0"/>
         <v>-75.516999999999996</v>
       </c>
       <c r="S197" s="10" t="s">
@@ -4010,7 +4010,7 @@
         <v>158477.728</v>
       </c>
       <c r="H198" s="8">
-        <f>F198</f>
+        <f t="shared" si="0"/>
         <v>158477.728</v>
       </c>
       <c r="S198" s="10" t="s">
@@ -4028,7 +4028,7 @@
         <v>295.30900000000003</v>
       </c>
       <c r="H199">
-        <f>F199</f>
+        <f t="shared" si="0"/>
         <v>295.30900000000003</v>
       </c>
       <c r="S199" s="10" t="s">
@@ -4046,7 +4046,7 @@
         <v>2702.27</v>
       </c>
       <c r="H200">
-        <f>F200</f>
+        <f t="shared" si="0"/>
         <v>2702.27</v>
       </c>
       <c r="S200" s="10" t="s">
@@ -4701,7 +4701,7 @@
         <v>16846.954000000002</v>
       </c>
       <c r="G279" s="5">
-        <f t="shared" ref="G279:G285" si="0">F279</f>
+        <f t="shared" ref="G279:G285" si="1">F279</f>
         <v>16846.954000000002</v>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
         <v>47059.222000000002</v>
       </c>
       <c r="G280" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47059.222000000002</v>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
         <v>-75.516999999999996</v>
       </c>
       <c r="G281" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-75.516999999999996</v>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
         <v>158477.728</v>
       </c>
       <c r="G282" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>158477.728</v>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
         <v>295.30900000000003</v>
       </c>
       <c r="G283" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>295.30900000000003</v>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
         <v>2702.27</v>
       </c>
       <c r="G284" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2702.27</v>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
         <v>1640293.358</v>
       </c>
       <c r="G285" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1640293.358</v>
       </c>
     </row>
